--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129996510</v>
       </c>
       <c r="B2" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,4398 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130041481</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79111</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>475411</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6830966</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130041437</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>475481</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6830882</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130041456</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79677</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>475534</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6830960</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130041441</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>475510</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6831109</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130041439</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>475435</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6831092</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130041495</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>475417</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6831034</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130041480</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79111</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>475568</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6831221</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130041515</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>475417</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6831034</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130041493</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>475504</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6831263</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130041455</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79677</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>475552</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6830976</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130041457</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79677</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>475451</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6830833</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130041514</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>475402</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6830990</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130041446</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79119</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>185</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>475549</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6830964</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130041517</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>475474</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6831123</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130041494</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>475448</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6830798</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130041497</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>475482</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6831123</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130041609</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78490</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>475502</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6831264</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130041610</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78490</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>475402</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6830990</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130041510</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>475448</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6830798</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130041504</v>
+      </c>
+      <c r="B22" t="n">
+        <v>81072</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>475493</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6831320</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130041511</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>475449</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6830820</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130041496</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>475435</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6831092</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130041559</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>475540</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6831162</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130041509</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>475484</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6830883</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130041513</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>475393</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6830875</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130041440</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>475486</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6831120</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130041505</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>475552</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6830976</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130041436</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>475501</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6831374</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130041561</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>475554</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6831117</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130041516</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>475433</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6831092</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130041438</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79706</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>475446</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6830798</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130041451</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79677</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>475501</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6831374</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130041454</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79677</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>475497</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6831311</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130041560</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>475581</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6831068</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130041512</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>475395</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6830844</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130041453</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79677</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>475492</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6831322</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130041452</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79677</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>475483</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6831329</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130041607</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78095</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>475568</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6831021</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130041557</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>475553</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6831206</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130041558</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>475533</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6831180</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130041503</v>
+      </c>
+      <c r="B43" t="n">
+        <v>81072</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>475473</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6831127</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129996510</v>
       </c>
       <c r="B2" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130041481</v>
       </c>
       <c r="B3" t="n">
-        <v>79111</v>
+        <v>79112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130041437</v>
+        <v>130041441</v>
       </c>
       <c r="B4" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475481</v>
+        <v>475510</v>
       </c>
       <c r="R4" t="n">
-        <v>6830882</v>
+        <v>6831109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041456</v>
+        <v>130041437</v>
       </c>
       <c r="B5" t="n">
-        <v>79677</v>
+        <v>79707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475534</v>
+        <v>475481</v>
       </c>
       <c r="R5" t="n">
-        <v>6830960</v>
+        <v>6830882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130041441</v>
+        <v>130041456</v>
       </c>
       <c r="B6" t="n">
-        <v>79706</v>
+        <v>79678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475510</v>
+        <v>475534</v>
       </c>
       <c r="R6" t="n">
-        <v>6831109</v>
+        <v>6830960</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130041439</v>
+        <v>130041495</v>
       </c>
       <c r="B7" t="n">
-        <v>79706</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475435</v>
+        <v>475417</v>
       </c>
       <c r="R7" t="n">
-        <v>6831092</v>
+        <v>6831034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041495</v>
+        <v>130041480</v>
       </c>
       <c r="B8" t="n">
-        <v>78845</v>
+        <v>79112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475417</v>
+        <v>475568</v>
       </c>
       <c r="R8" t="n">
-        <v>6831034</v>
+        <v>6831221</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041480</v>
+        <v>130041439</v>
       </c>
       <c r="B9" t="n">
-        <v>79111</v>
+        <v>79707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475568</v>
+        <v>475435</v>
       </c>
       <c r="R9" t="n">
-        <v>6831221</v>
+        <v>6831092</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041515</v>
+        <v>130041493</v>
       </c>
       <c r="B10" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475417</v>
+        <v>475504</v>
       </c>
       <c r="R10" t="n">
-        <v>6831034</v>
+        <v>6831263</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130041493</v>
+        <v>130041455</v>
       </c>
       <c r="B11" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475504</v>
+        <v>475552</v>
       </c>
       <c r="R11" t="n">
-        <v>6831263</v>
+        <v>6830976</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130041455</v>
+        <v>130041515</v>
       </c>
       <c r="B12" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475552</v>
+        <v>475417</v>
       </c>
       <c r="R12" t="n">
-        <v>6830976</v>
+        <v>6831034</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041457</v>
+        <v>130041446</v>
       </c>
       <c r="B13" t="n">
-        <v>79677</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475451</v>
+        <v>475549</v>
       </c>
       <c r="R13" t="n">
-        <v>6830833</v>
+        <v>6830964</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1962,7 @@
         <v>130041514</v>
       </c>
       <c r="B14" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041446</v>
+        <v>130041517</v>
       </c>
       <c r="B15" t="n">
-        <v>79119</v>
+        <v>78845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475549</v>
+        <v>475474</v>
       </c>
       <c r="R15" t="n">
-        <v>6830964</v>
+        <v>6831123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041517</v>
+        <v>130041609</v>
       </c>
       <c r="B16" t="n">
-        <v>78844</v>
+        <v>78491</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475474</v>
+        <v>475502</v>
       </c>
       <c r="R16" t="n">
-        <v>6831123</v>
+        <v>6831264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2283,7 @@
         <v>130041494</v>
       </c>
       <c r="B17" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>130041497</v>
       </c>
       <c r="B18" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130041609</v>
+        <v>130041457</v>
       </c>
       <c r="B19" t="n">
-        <v>78490</v>
+        <v>79678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475502</v>
+        <v>475451</v>
       </c>
       <c r="R19" t="n">
-        <v>6831264</v>
+        <v>6830833</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2604,7 @@
         <v>130041610</v>
       </c>
       <c r="B20" t="n">
-        <v>78490</v>
+        <v>78491</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>130041510</v>
       </c>
       <c r="B21" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>130041504</v>
       </c>
       <c r="B22" t="n">
-        <v>81072</v>
+        <v>81073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>130041511</v>
       </c>
       <c r="B23" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130041496</v>
+        <v>130041559</v>
       </c>
       <c r="B24" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475435</v>
+        <v>475540</v>
       </c>
       <c r="R24" t="n">
-        <v>6831092</v>
+        <v>6831162</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130041559</v>
+        <v>130041496</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475540</v>
+        <v>475435</v>
       </c>
       <c r="R25" t="n">
-        <v>6831162</v>
+        <v>6831092</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,7 +3246,7 @@
         <v>130041509</v>
       </c>
       <c r="B26" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>130041513</v>
       </c>
       <c r="B27" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>130041440</v>
       </c>
       <c r="B28" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130041505</v>
+        <v>130041436</v>
       </c>
       <c r="B29" t="n">
-        <v>78844</v>
+        <v>79707</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,39 +3575,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475552</v>
+        <v>475501</v>
       </c>
       <c r="R29" t="n">
-        <v>6830976</v>
+        <v>6831374</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3649,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3676,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130041436</v>
+        <v>130041505</v>
       </c>
       <c r="B30" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3687,34 +3682,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475501</v>
+        <v>475552</v>
       </c>
       <c r="R30" t="n">
-        <v>6831374</v>
+        <v>6830976</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3786,7 +3786,7 @@
         <v>130041561</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>130041516</v>
       </c>
       <c r="B32" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>130041438</v>
       </c>
       <c r="B33" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130041451</v>
+        <v>130041560</v>
       </c>
       <c r="B34" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4115,21 +4115,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475501</v>
+        <v>475581</v>
       </c>
       <c r="R34" t="n">
-        <v>6831374</v>
+        <v>6831068</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4211,10 +4211,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130041454</v>
+        <v>130041451</v>
       </c>
       <c r="B35" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475497</v>
+        <v>475501</v>
       </c>
       <c r="R35" t="n">
-        <v>6831311</v>
+        <v>6831374</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4318,10 +4318,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130041560</v>
+        <v>130041454</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4329,21 +4329,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475581</v>
+        <v>475497</v>
       </c>
       <c r="R36" t="n">
-        <v>6831068</v>
+        <v>6831311</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4428,7 +4428,7 @@
         <v>130041512</v>
       </c>
       <c r="B37" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>130041453</v>
       </c>
       <c r="B38" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>130041452</v>
       </c>
       <c r="B39" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4746,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130041607</v>
+        <v>130041557</v>
       </c>
       <c r="B40" t="n">
-        <v>78095</v>
+        <v>79088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4757,21 +4757,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475568</v>
+        <v>475553</v>
       </c>
       <c r="R40" t="n">
-        <v>6831021</v>
+        <v>6831206</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130041557</v>
+        <v>130041607</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>78095</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475553</v>
+        <v>475568</v>
       </c>
       <c r="R41" t="n">
-        <v>6831206</v>
+        <v>6831021</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4960,10 +4960,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130041558</v>
+        <v>130041503</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>81073</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4971,21 +4971,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475533</v>
+        <v>475473</v>
       </c>
       <c r="R42" t="n">
-        <v>6831180</v>
+        <v>6831127</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5067,10 +5067,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130041503</v>
+        <v>130041558</v>
       </c>
       <c r="B43" t="n">
-        <v>81072</v>
+        <v>79088</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5078,21 +5078,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475473</v>
+        <v>475533</v>
       </c>
       <c r="R43" t="n">
-        <v>6831127</v>
+        <v>6831180</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5171,6 +5171,1630 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130044601</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79678</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>475483</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6831369</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130044665</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>475435</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6831137</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130044586</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>475506</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6831387</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130044604</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>475483</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6831369</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130044657</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>475450</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6831186</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130044587</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>475483</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6831369</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130044636</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>475460</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6831232</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130044631</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79678</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>475472</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6831247</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130044585</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>475506</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6831387</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130044628</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>475460</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6831267</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130044669</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>475501</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6831118</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130044651</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79678</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>475450</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6831186</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130044663</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>475421</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6831144</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130044623</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>475460</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6831267</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130044615</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57844</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>475444</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6831288</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130044660</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78845</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>475447</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6831162</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130041495</v>
+        <v>130041480</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>79112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475417</v>
+        <v>475568</v>
       </c>
       <c r="R7" t="n">
-        <v>6831034</v>
+        <v>6831221</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041480</v>
+        <v>130041495</v>
       </c>
       <c r="B8" t="n">
-        <v>79112</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475568</v>
+        <v>475417</v>
       </c>
       <c r="R8" t="n">
-        <v>6831221</v>
+        <v>6831034</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130041436</v>
+        <v>130041505</v>
       </c>
       <c r="B29" t="n">
-        <v>79707</v>
+        <v>78845</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,34 +3575,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475501</v>
+        <v>475552</v>
       </c>
       <c r="R29" t="n">
-        <v>6831374</v>
+        <v>6830976</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3639,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3649,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,10 +3676,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130041505</v>
+        <v>130041561</v>
       </c>
       <c r="B30" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,39 +3687,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475552</v>
+        <v>475554</v>
       </c>
       <c r="R30" t="n">
-        <v>6830976</v>
+        <v>6831117</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130041561</v>
+        <v>130041516</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475554</v>
+        <v>475433</v>
       </c>
       <c r="R31" t="n">
-        <v>6831117</v>
+        <v>6831092</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3890,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130041516</v>
+        <v>130041436</v>
       </c>
       <c r="B32" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475433</v>
+        <v>475501</v>
       </c>
       <c r="R32" t="n">
-        <v>6831092</v>
+        <v>6831374</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4960,10 +4960,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130041503</v>
+        <v>130041558</v>
       </c>
       <c r="B42" t="n">
-        <v>81073</v>
+        <v>79088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4971,21 +4971,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475473</v>
+        <v>475533</v>
       </c>
       <c r="R42" t="n">
-        <v>6831127</v>
+        <v>6831180</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5067,10 +5067,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130041558</v>
+        <v>130041503</v>
       </c>
       <c r="B43" t="n">
-        <v>79088</v>
+        <v>81073</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5078,21 +5078,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475533</v>
+        <v>475473</v>
       </c>
       <c r="R43" t="n">
-        <v>6831180</v>
+        <v>6831127</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130041480</v>
+        <v>130041495</v>
       </c>
       <c r="B7" t="n">
-        <v>79112</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475568</v>
+        <v>475417</v>
       </c>
       <c r="R7" t="n">
-        <v>6831221</v>
+        <v>6831034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041495</v>
+        <v>130041480</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>79112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475417</v>
+        <v>475568</v>
       </c>
       <c r="R8" t="n">
-        <v>6831034</v>
+        <v>6831221</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041493</v>
+        <v>130041515</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>78845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475504</v>
+        <v>475417</v>
       </c>
       <c r="R10" t="n">
-        <v>6831263</v>
+        <v>6831034</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130041455</v>
+        <v>130041493</v>
       </c>
       <c r="B11" t="n">
-        <v>79678</v>
+        <v>78846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475552</v>
+        <v>475504</v>
       </c>
       <c r="R11" t="n">
-        <v>6830976</v>
+        <v>6831263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130041515</v>
+        <v>130041455</v>
       </c>
       <c r="B12" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475417</v>
+        <v>475552</v>
       </c>
       <c r="R12" t="n">
-        <v>6831034</v>
+        <v>6830976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130041504</v>
+        <v>130041511</v>
       </c>
       <c r="B22" t="n">
-        <v>81073</v>
+        <v>78845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475493</v>
+        <v>475449</v>
       </c>
       <c r="R22" t="n">
-        <v>6831320</v>
+        <v>6830820</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041511</v>
+        <v>130041504</v>
       </c>
       <c r="B23" t="n">
-        <v>78845</v>
+        <v>81073</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475449</v>
+        <v>475493</v>
       </c>
       <c r="R23" t="n">
-        <v>6830820</v>
+        <v>6831320</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130041505</v>
+        <v>130041436</v>
       </c>
       <c r="B29" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,39 +3575,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475552</v>
+        <v>475501</v>
       </c>
       <c r="R29" t="n">
-        <v>6830976</v>
+        <v>6831374</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3649,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3676,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130041561</v>
+        <v>130041505</v>
       </c>
       <c r="B30" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3687,34 +3682,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475554</v>
+        <v>475552</v>
       </c>
       <c r="R30" t="n">
-        <v>6831117</v>
+        <v>6830976</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130041516</v>
+        <v>130041561</v>
       </c>
       <c r="B31" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475433</v>
+        <v>475554</v>
       </c>
       <c r="R31" t="n">
-        <v>6831092</v>
+        <v>6831117</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3890,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130041436</v>
+        <v>130041516</v>
       </c>
       <c r="B32" t="n">
-        <v>79707</v>
+        <v>78845</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475501</v>
+        <v>475433</v>
       </c>
       <c r="R32" t="n">
-        <v>6831374</v>
+        <v>6831092</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4960,10 +4960,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130041558</v>
+        <v>130041503</v>
       </c>
       <c r="B42" t="n">
-        <v>79088</v>
+        <v>81073</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4971,21 +4971,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475533</v>
+        <v>475473</v>
       </c>
       <c r="R42" t="n">
-        <v>6831180</v>
+        <v>6831127</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5067,10 +5067,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130041503</v>
+        <v>130041558</v>
       </c>
       <c r="B43" t="n">
-        <v>81073</v>
+        <v>79088</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5078,21 +5078,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475473</v>
+        <v>475533</v>
       </c>
       <c r="R43" t="n">
-        <v>6831127</v>
+        <v>6831180</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129996510</v>
       </c>
       <c r="B2" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130041481</v>
       </c>
       <c r="B3" t="n">
-        <v>79112</v>
+        <v>79113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130041441</v>
+        <v>130041437</v>
       </c>
       <c r="B4" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475510</v>
+        <v>475481</v>
       </c>
       <c r="R4" t="n">
-        <v>6831109</v>
+        <v>6830882</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041437</v>
+        <v>130041441</v>
       </c>
       <c r="B5" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475481</v>
+        <v>475510</v>
       </c>
       <c r="R5" t="n">
-        <v>6830882</v>
+        <v>6831109</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>130041456</v>
       </c>
       <c r="B6" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130041495</v>
+        <v>130041439</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>79708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475417</v>
+        <v>475435</v>
       </c>
       <c r="R7" t="n">
-        <v>6831034</v>
+        <v>6831092</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>130041480</v>
       </c>
       <c r="B8" t="n">
-        <v>79112</v>
+        <v>79113</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041439</v>
+        <v>130041495</v>
       </c>
       <c r="B9" t="n">
-        <v>79707</v>
+        <v>78847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475435</v>
+        <v>475417</v>
       </c>
       <c r="R9" t="n">
-        <v>6831092</v>
+        <v>6831034</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1534,7 @@
         <v>130041515</v>
       </c>
       <c r="B10" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>130041493</v>
       </c>
       <c r="B11" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130041455</v>
       </c>
       <c r="B12" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041446</v>
+        <v>130041494</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>78847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475549</v>
+        <v>475448</v>
       </c>
       <c r="R13" t="n">
-        <v>6830964</v>
+        <v>6830798</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041514</v>
+        <v>130041497</v>
       </c>
       <c r="B14" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475402</v>
+        <v>475482</v>
       </c>
       <c r="R14" t="n">
-        <v>6830990</v>
+        <v>6831123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041517</v>
+        <v>130041514</v>
       </c>
       <c r="B15" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475474</v>
+        <v>475402</v>
       </c>
       <c r="R15" t="n">
-        <v>6831123</v>
+        <v>6830990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041609</v>
+        <v>130041517</v>
       </c>
       <c r="B16" t="n">
-        <v>78491</v>
+        <v>78846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475502</v>
+        <v>475474</v>
       </c>
       <c r="R16" t="n">
-        <v>6831264</v>
+        <v>6831123</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041494</v>
+        <v>130041609</v>
       </c>
       <c r="B17" t="n">
-        <v>78846</v>
+        <v>78492</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475448</v>
+        <v>475502</v>
       </c>
       <c r="R17" t="n">
-        <v>6830798</v>
+        <v>6831264</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041497</v>
+        <v>130041446</v>
       </c>
       <c r="B18" t="n">
-        <v>78846</v>
+        <v>79121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475482</v>
+        <v>475549</v>
       </c>
       <c r="R18" t="n">
-        <v>6831123</v>
+        <v>6830964</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2497,7 @@
         <v>130041457</v>
       </c>
       <c r="B19" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>130041610</v>
       </c>
       <c r="B20" t="n">
-        <v>78491</v>
+        <v>78492</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>130041510</v>
       </c>
       <c r="B21" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130041511</v>
+        <v>130041504</v>
       </c>
       <c r="B22" t="n">
-        <v>78845</v>
+        <v>81074</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475449</v>
+        <v>475493</v>
       </c>
       <c r="R22" t="n">
-        <v>6830820</v>
+        <v>6831320</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041504</v>
+        <v>130041511</v>
       </c>
       <c r="B23" t="n">
-        <v>81073</v>
+        <v>78846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475493</v>
+        <v>475449</v>
       </c>
       <c r="R23" t="n">
-        <v>6831320</v>
+        <v>6830820</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3032,7 @@
         <v>130041559</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>130041496</v>
       </c>
       <c r="B25" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>130041509</v>
       </c>
       <c r="B26" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>130041513</v>
       </c>
       <c r="B27" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>130041440</v>
       </c>
       <c r="B28" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130041436</v>
+        <v>130041505</v>
       </c>
       <c r="B29" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,34 +3575,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475501</v>
+        <v>475552</v>
       </c>
       <c r="R29" t="n">
-        <v>6831374</v>
+        <v>6830976</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3639,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3649,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,10 +3676,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130041505</v>
+        <v>130041436</v>
       </c>
       <c r="B30" t="n">
-        <v>78845</v>
+        <v>79708</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,39 +3687,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475552</v>
+        <v>475501</v>
       </c>
       <c r="R30" t="n">
-        <v>6830976</v>
+        <v>6831374</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130041561</v>
+        <v>130041516</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475554</v>
+        <v>475433</v>
       </c>
       <c r="R31" t="n">
-        <v>6831117</v>
+        <v>6831092</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3890,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130041516</v>
+        <v>130041561</v>
       </c>
       <c r="B32" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475433</v>
+        <v>475554</v>
       </c>
       <c r="R32" t="n">
-        <v>6831092</v>
+        <v>6831117</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4000,7 +4000,7 @@
         <v>130041438</v>
       </c>
       <c r="B33" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130041560</v>
+        <v>130041451</v>
       </c>
       <c r="B34" t="n">
-        <v>79088</v>
+        <v>79679</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4115,21 +4115,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475581</v>
+        <v>475501</v>
       </c>
       <c r="R34" t="n">
-        <v>6831068</v>
+        <v>6831374</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4211,10 +4211,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130041451</v>
+        <v>130041454</v>
       </c>
       <c r="B35" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475501</v>
+        <v>475497</v>
       </c>
       <c r="R35" t="n">
-        <v>6831374</v>
+        <v>6831311</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4318,10 +4318,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130041454</v>
+        <v>130041560</v>
       </c>
       <c r="B36" t="n">
-        <v>79678</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4329,21 +4329,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475497</v>
+        <v>475581</v>
       </c>
       <c r="R36" t="n">
-        <v>6831311</v>
+        <v>6831068</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4428,7 +4428,7 @@
         <v>130041512</v>
       </c>
       <c r="B37" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4532,10 +4532,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130041453</v>
+        <v>130041607</v>
       </c>
       <c r="B38" t="n">
-        <v>79678</v>
+        <v>78096</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4543,21 +4543,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475492</v>
+        <v>475568</v>
       </c>
       <c r="R38" t="n">
-        <v>6831322</v>
+        <v>6831021</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,10 +4639,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130041452</v>
+        <v>130041453</v>
       </c>
       <c r="B39" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475483</v>
+        <v>475492</v>
       </c>
       <c r="R39" t="n">
-        <v>6831329</v>
+        <v>6831322</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4746,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130041557</v>
+        <v>130041452</v>
       </c>
       <c r="B40" t="n">
-        <v>79088</v>
+        <v>79679</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4757,21 +4757,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475553</v>
+        <v>475483</v>
       </c>
       <c r="R40" t="n">
-        <v>6831206</v>
+        <v>6831329</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130041607</v>
+        <v>130041557</v>
       </c>
       <c r="B41" t="n">
-        <v>78095</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475568</v>
+        <v>475553</v>
       </c>
       <c r="R41" t="n">
-        <v>6831021</v>
+        <v>6831206</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4963,7 +4963,7 @@
         <v>130041503</v>
       </c>
       <c r="B42" t="n">
-        <v>81073</v>
+        <v>81074</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>130041558</v>
       </c>
       <c r="B43" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130044601</v>
+        <v>130044586</v>
       </c>
       <c r="B44" t="n">
-        <v>79678</v>
+        <v>79708</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5185,21 +5185,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475483</v>
+        <v>475506</v>
       </c>
       <c r="R44" t="n">
-        <v>6831369</v>
+        <v>6831387</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5380,10 +5380,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130044586</v>
+        <v>130044601</v>
       </c>
       <c r="B46" t="n">
-        <v>79707</v>
+        <v>79679</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5391,21 +5391,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475506</v>
+        <v>475483</v>
       </c>
       <c r="R46" t="n">
-        <v>6831387</v>
+        <v>6831369</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5484,7 +5484,7 @@
         <v>130044604</v>
       </c>
       <c r="B47" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>130044657</v>
       </c>
       <c r="B48" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>130044587</v>
       </c>
       <c r="B49" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>130044636</v>
       </c>
       <c r="B50" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>130044631</v>
       </c>
       <c r="B51" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>130044585</v>
       </c>
       <c r="B52" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>130044628</v>
       </c>
       <c r="B53" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>130044669</v>
       </c>
       <c r="B54" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>130044651</v>
       </c>
       <c r="B55" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>130044663</v>
       </c>
       <c r="B56" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>130044623</v>
       </c>
       <c r="B57" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6592,42 +6592,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130044615</v>
+        <v>130044660</v>
       </c>
       <c r="B58" t="n">
-        <v>57844</v>
+        <v>78846</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6635,10 +6630,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475444</v>
+        <v>475447</v>
       </c>
       <c r="R58" t="n">
-        <v>6831288</v>
+        <v>6831162</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6679,6 +6674,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6697,37 +6693,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130044660</v>
+        <v>130044615</v>
       </c>
       <c r="B59" t="n">
-        <v>78845</v>
+        <v>57844</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6735,10 +6736,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>475447</v>
+        <v>475444</v>
       </c>
       <c r="R59" t="n">
-        <v>6831162</v>
+        <v>6831288</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6779,7 +6780,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041493</v>
+        <v>130041515</v>
       </c>
       <c r="B10" t="n">
-        <v>78853</v>
+        <v>78852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475504</v>
+        <v>475417</v>
       </c>
       <c r="R10" t="n">
-        <v>6831263</v>
+        <v>6831034</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130041455</v>
+        <v>130041493</v>
       </c>
       <c r="B11" t="n">
-        <v>79685</v>
+        <v>78853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475552</v>
+        <v>475504</v>
       </c>
       <c r="R11" t="n">
-        <v>6830976</v>
+        <v>6831263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130041515</v>
+        <v>130041455</v>
       </c>
       <c r="B12" t="n">
-        <v>78852</v>
+        <v>79685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475417</v>
+        <v>475552</v>
       </c>
       <c r="R12" t="n">
-        <v>6831034</v>
+        <v>6830976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041514</v>
+        <v>130041497</v>
       </c>
       <c r="B13" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475402</v>
+        <v>475482</v>
       </c>
       <c r="R13" t="n">
-        <v>6830990</v>
+        <v>6831123</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041517</v>
+        <v>130041514</v>
       </c>
       <c r="B14" t="n">
         <v>78852</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475474</v>
+        <v>475402</v>
       </c>
       <c r="R14" t="n">
-        <v>6831123</v>
+        <v>6830990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041609</v>
+        <v>130041517</v>
       </c>
       <c r="B15" t="n">
-        <v>78498</v>
+        <v>78852</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475502</v>
+        <v>475474</v>
       </c>
       <c r="R15" t="n">
-        <v>6831264</v>
+        <v>6831123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041446</v>
+        <v>130041609</v>
       </c>
       <c r="B16" t="n">
-        <v>79127</v>
+        <v>78498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475549</v>
+        <v>475502</v>
       </c>
       <c r="R16" t="n">
-        <v>6830964</v>
+        <v>6831264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041457</v>
+        <v>130041446</v>
       </c>
       <c r="B17" t="n">
-        <v>79685</v>
+        <v>79127</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475451</v>
+        <v>475549</v>
       </c>
       <c r="R17" t="n">
-        <v>6830833</v>
+        <v>6830964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041494</v>
+        <v>130041457</v>
       </c>
       <c r="B18" t="n">
-        <v>78853</v>
+        <v>79685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475448</v>
+        <v>475451</v>
       </c>
       <c r="R18" t="n">
-        <v>6830798</v>
+        <v>6830833</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130041497</v>
+        <v>130041494</v>
       </c>
       <c r="B19" t="n">
         <v>78853</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475482</v>
+        <v>475448</v>
       </c>
       <c r="R19" t="n">
-        <v>6831123</v>
+        <v>6830798</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130041511</v>
+        <v>130041504</v>
       </c>
       <c r="B22" t="n">
-        <v>78852</v>
+        <v>81080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475449</v>
+        <v>475493</v>
       </c>
       <c r="R22" t="n">
-        <v>6830820</v>
+        <v>6831320</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041504</v>
+        <v>130041511</v>
       </c>
       <c r="B23" t="n">
-        <v>81080</v>
+        <v>78852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475493</v>
+        <v>475449</v>
       </c>
       <c r="R23" t="n">
-        <v>6831320</v>
+        <v>6830820</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130041496</v>
+        <v>130041559</v>
       </c>
       <c r="B24" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475435</v>
+        <v>475540</v>
       </c>
       <c r="R24" t="n">
-        <v>6831092</v>
+        <v>6831162</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130041559</v>
+        <v>130041496</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475540</v>
+        <v>475435</v>
       </c>
       <c r="R25" t="n">
-        <v>6831162</v>
+        <v>6831092</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130044601</v>
+        <v>130044586</v>
       </c>
       <c r="B44" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5185,21 +5185,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475483</v>
+        <v>475506</v>
       </c>
       <c r="R44" t="n">
-        <v>6831369</v>
+        <v>6831387</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130044586</v>
+        <v>130044665</v>
       </c>
       <c r="B45" t="n">
-        <v>79714</v>
+        <v>57741</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5286,26 +5286,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5313,10 +5318,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475506</v>
+        <v>475435</v>
       </c>
       <c r="R45" t="n">
-        <v>6831387</v>
+        <v>6831137</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5357,7 +5362,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5376,10 +5380,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130044665</v>
+        <v>130044601</v>
       </c>
       <c r="B46" t="n">
-        <v>57741</v>
+        <v>79685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5387,31 +5391,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5419,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475435</v>
+        <v>475483</v>
       </c>
       <c r="R46" t="n">
-        <v>6831137</v>
+        <v>6831369</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5463,6 +5462,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041497</v>
+        <v>130041514</v>
       </c>
       <c r="B13" t="n">
-        <v>78853</v>
+        <v>78852</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475482</v>
+        <v>475402</v>
       </c>
       <c r="R13" t="n">
-        <v>6831123</v>
+        <v>6830990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041514</v>
+        <v>130041517</v>
       </c>
       <c r="B14" t="n">
         <v>78852</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475402</v>
+        <v>475474</v>
       </c>
       <c r="R14" t="n">
-        <v>6830990</v>
+        <v>6831123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041517</v>
+        <v>130041609</v>
       </c>
       <c r="B15" t="n">
-        <v>78852</v>
+        <v>78498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475474</v>
+        <v>475502</v>
       </c>
       <c r="R15" t="n">
-        <v>6831123</v>
+        <v>6831264</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041609</v>
+        <v>130041446</v>
       </c>
       <c r="B16" t="n">
-        <v>78498</v>
+        <v>79127</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475502</v>
+        <v>475549</v>
       </c>
       <c r="R16" t="n">
-        <v>6831264</v>
+        <v>6830964</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041446</v>
+        <v>130041457</v>
       </c>
       <c r="B17" t="n">
-        <v>79127</v>
+        <v>79685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475549</v>
+        <v>475451</v>
       </c>
       <c r="R17" t="n">
-        <v>6830964</v>
+        <v>6830833</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041457</v>
+        <v>130041494</v>
       </c>
       <c r="B18" t="n">
-        <v>79685</v>
+        <v>78853</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475451</v>
+        <v>475448</v>
       </c>
       <c r="R18" t="n">
-        <v>6830833</v>
+        <v>6830798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130041494</v>
+        <v>130041497</v>
       </c>
       <c r="B19" t="n">
         <v>78853</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475448</v>
+        <v>475482</v>
       </c>
       <c r="R19" t="n">
-        <v>6830798</v>
+        <v>6831123</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130041559</v>
+        <v>130041496</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475540</v>
+        <v>475435</v>
       </c>
       <c r="R24" t="n">
-        <v>6831162</v>
+        <v>6831092</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130041496</v>
+        <v>130041559</v>
       </c>
       <c r="B25" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475435</v>
+        <v>475540</v>
       </c>
       <c r="R25" t="n">
-        <v>6831092</v>
+        <v>6831162</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4532,10 +4532,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130041607</v>
+        <v>130041557</v>
       </c>
       <c r="B38" t="n">
-        <v>78102</v>
+        <v>79095</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4543,21 +4543,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475568</v>
+        <v>475553</v>
       </c>
       <c r="R38" t="n">
-        <v>6831021</v>
+        <v>6831206</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,10 +4639,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130041453</v>
+        <v>130041607</v>
       </c>
       <c r="B39" t="n">
-        <v>79685</v>
+        <v>78102</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4650,21 +4650,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475492</v>
+        <v>475568</v>
       </c>
       <c r="R39" t="n">
-        <v>6831322</v>
+        <v>6831021</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4746,7 +4746,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130041452</v>
+        <v>130041453</v>
       </c>
       <c r="B40" t="n">
         <v>79685</v>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475483</v>
+        <v>475492</v>
       </c>
       <c r="R40" t="n">
-        <v>6831329</v>
+        <v>6831322</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130041557</v>
+        <v>130041452</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475553</v>
+        <v>475483</v>
       </c>
       <c r="R41" t="n">
-        <v>6831206</v>
+        <v>6831329</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130041456</v>
+        <v>130041441</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475534</v>
+        <v>475510</v>
       </c>
       <c r="R4" t="n">
-        <v>6830960</v>
+        <v>6831109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130041441</v>
+        <v>130041456</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475510</v>
+        <v>475534</v>
       </c>
       <c r="R6" t="n">
-        <v>6831109</v>
+        <v>6830960</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130041480</v>
+        <v>130041495</v>
       </c>
       <c r="B7" t="n">
-        <v>79119</v>
+        <v>78853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475568</v>
+        <v>475417</v>
       </c>
       <c r="R7" t="n">
-        <v>6831221</v>
+        <v>6831034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041495</v>
+        <v>130041480</v>
       </c>
       <c r="B9" t="n">
-        <v>78853</v>
+        <v>79119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475417</v>
+        <v>475568</v>
       </c>
       <c r="R9" t="n">
-        <v>6831034</v>
+        <v>6831221</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041514</v>
+        <v>130041457</v>
       </c>
       <c r="B13" t="n">
-        <v>78852</v>
+        <v>79685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475402</v>
+        <v>475451</v>
       </c>
       <c r="R13" t="n">
-        <v>6830990</v>
+        <v>6830833</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041517</v>
+        <v>130041494</v>
       </c>
       <c r="B14" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475474</v>
+        <v>475448</v>
       </c>
       <c r="R14" t="n">
-        <v>6831123</v>
+        <v>6830798</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041609</v>
+        <v>130041497</v>
       </c>
       <c r="B15" t="n">
-        <v>78498</v>
+        <v>78853</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475502</v>
+        <v>475482</v>
       </c>
       <c r="R15" t="n">
-        <v>6831264</v>
+        <v>6831123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041446</v>
+        <v>130041609</v>
       </c>
       <c r="B16" t="n">
-        <v>79127</v>
+        <v>78498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475549</v>
+        <v>475502</v>
       </c>
       <c r="R16" t="n">
-        <v>6830964</v>
+        <v>6831264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041457</v>
+        <v>130041446</v>
       </c>
       <c r="B17" t="n">
-        <v>79685</v>
+        <v>79127</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475451</v>
+        <v>475549</v>
       </c>
       <c r="R17" t="n">
-        <v>6830833</v>
+        <v>6830964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041494</v>
+        <v>130041517</v>
       </c>
       <c r="B18" t="n">
-        <v>78853</v>
+        <v>78852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475448</v>
+        <v>475474</v>
       </c>
       <c r="R18" t="n">
-        <v>6830798</v>
+        <v>6831123</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130041497</v>
+        <v>130041514</v>
       </c>
       <c r="B19" t="n">
-        <v>78853</v>
+        <v>78852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475482</v>
+        <v>475402</v>
       </c>
       <c r="R19" t="n">
-        <v>6831123</v>
+        <v>6830990</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130041610</v>
+        <v>130041510</v>
       </c>
       <c r="B20" t="n">
-        <v>78498</v>
+        <v>78852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475402</v>
+        <v>475448</v>
       </c>
       <c r="R20" t="n">
-        <v>6830990</v>
+        <v>6830798</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130041510</v>
+        <v>130041610</v>
       </c>
       <c r="B21" t="n">
-        <v>78852</v>
+        <v>78498</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475448</v>
+        <v>475402</v>
       </c>
       <c r="R21" t="n">
-        <v>6830798</v>
+        <v>6830990</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3243,7 +3243,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130041509</v>
+        <v>130041513</v>
       </c>
       <c r="B26" t="n">
         <v>78852</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475484</v>
+        <v>475393</v>
       </c>
       <c r="R26" t="n">
-        <v>6830883</v>
+        <v>6830875</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130041513</v>
+        <v>130041509</v>
       </c>
       <c r="B27" t="n">
         <v>78852</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475393</v>
+        <v>475484</v>
       </c>
       <c r="R27" t="n">
-        <v>6830875</v>
+        <v>6830883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,7 +3564,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130041505</v>
+        <v>130041516</v>
       </c>
       <c r="B29" t="n">
         <v>78852</v>
@@ -3593,21 +3593,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475552</v>
+        <v>475433</v>
       </c>
       <c r="R29" t="n">
-        <v>6830976</v>
+        <v>6831092</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3649,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3676,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130041561</v>
+        <v>130041436</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3687,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3711,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475554</v>
+        <v>475501</v>
       </c>
       <c r="R30" t="n">
-        <v>6831117</v>
+        <v>6831374</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3746,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3756,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3783,7 +3778,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130041516</v>
+        <v>130041505</v>
       </c>
       <c r="B31" t="n">
         <v>78852</v>
@@ -3812,16 +3807,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475433</v>
+        <v>475552</v>
       </c>
       <c r="R31" t="n">
-        <v>6831092</v>
+        <v>6830976</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3890,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130041436</v>
+        <v>130041561</v>
       </c>
       <c r="B32" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475501</v>
+        <v>475554</v>
       </c>
       <c r="R32" t="n">
-        <v>6831374</v>
+        <v>6831117</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4532,10 +4532,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130041557</v>
+        <v>130041453</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4543,21 +4543,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475553</v>
+        <v>475492</v>
       </c>
       <c r="R38" t="n">
-        <v>6831206</v>
+        <v>6831322</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,10 +4639,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130041607</v>
+        <v>130041452</v>
       </c>
       <c r="B39" t="n">
-        <v>78102</v>
+        <v>79685</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4650,21 +4650,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475568</v>
+        <v>475483</v>
       </c>
       <c r="R39" t="n">
-        <v>6831021</v>
+        <v>6831329</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130041453</v>
+        <v>130041607</v>
       </c>
       <c r="B40" t="n">
-        <v>79685</v>
+        <v>78102</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4757,21 +4757,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475492</v>
+        <v>475568</v>
       </c>
       <c r="R40" t="n">
-        <v>6831322</v>
+        <v>6831021</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,10 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130041452</v>
+        <v>130041557</v>
       </c>
       <c r="B41" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475483</v>
+        <v>475553</v>
       </c>
       <c r="R41" t="n">
-        <v>6831329</v>
+        <v>6831206</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6289,10 +6289,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130044651</v>
+        <v>130044663</v>
       </c>
       <c r="B55" t="n">
-        <v>79685</v>
+        <v>78852</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6300,21 +6300,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475450</v>
+        <v>475421</v>
       </c>
       <c r="R55" t="n">
-        <v>6831186</v>
+        <v>6831144</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130044663</v>
+        <v>130044651</v>
       </c>
       <c r="B56" t="n">
-        <v>78852</v>
+        <v>79685</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6401,21 +6401,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6428,10 +6428,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475421</v>
+        <v>475450</v>
       </c>
       <c r="R56" t="n">
-        <v>6831144</v>
+        <v>6831186</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6592,37 +6592,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130044660</v>
+        <v>130044615</v>
       </c>
       <c r="B58" t="n">
-        <v>78852</v>
+        <v>57845</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6630,10 +6635,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475447</v>
+        <v>475444</v>
       </c>
       <c r="R58" t="n">
-        <v>6831162</v>
+        <v>6831288</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6674,7 +6679,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6693,42 +6697,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130044615</v>
+        <v>130044660</v>
       </c>
       <c r="B59" t="n">
-        <v>57845</v>
+        <v>78852</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6736,10 +6735,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>475444</v>
+        <v>475447</v>
       </c>
       <c r="R59" t="n">
-        <v>6831288</v>
+        <v>6831162</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6780,6 +6779,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129996510</v>
       </c>
       <c r="B2" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130041481</v>
       </c>
       <c r="B3" t="n">
-        <v>79119</v>
+        <v>79204</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130041441</v>
+        <v>130041437</v>
       </c>
       <c r="B4" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475510</v>
+        <v>475481</v>
       </c>
       <c r="R4" t="n">
-        <v>6831109</v>
+        <v>6830882</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041437</v>
+        <v>130041456</v>
       </c>
       <c r="B5" t="n">
-        <v>79714</v>
+        <v>79770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475481</v>
+        <v>475534</v>
       </c>
       <c r="R5" t="n">
-        <v>6830882</v>
+        <v>6830960</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130041456</v>
+        <v>130041441</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>79799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475534</v>
+        <v>475510</v>
       </c>
       <c r="R6" t="n">
-        <v>6830960</v>
+        <v>6831109</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130041495</v>
+        <v>130041439</v>
       </c>
       <c r="B7" t="n">
-        <v>78853</v>
+        <v>79799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475417</v>
+        <v>475435</v>
       </c>
       <c r="R7" t="n">
-        <v>6831034</v>
+        <v>6831092</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041439</v>
+        <v>130041495</v>
       </c>
       <c r="B8" t="n">
-        <v>79714</v>
+        <v>78938</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475435</v>
+        <v>475417</v>
       </c>
       <c r="R8" t="n">
-        <v>6831092</v>
+        <v>6831034</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>130041480</v>
       </c>
       <c r="B9" t="n">
-        <v>79119</v>
+        <v>79204</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130041515</v>
       </c>
       <c r="B10" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>130041493</v>
       </c>
       <c r="B11" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130041455</v>
       </c>
       <c r="B12" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>130041457</v>
       </c>
       <c r="B13" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041494</v>
+        <v>130041514</v>
       </c>
       <c r="B14" t="n">
-        <v>78853</v>
+        <v>78937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475448</v>
+        <v>475402</v>
       </c>
       <c r="R14" t="n">
-        <v>6830798</v>
+        <v>6830990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041497</v>
+        <v>130041446</v>
       </c>
       <c r="B15" t="n">
-        <v>78853</v>
+        <v>79212</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475482</v>
+        <v>475549</v>
       </c>
       <c r="R15" t="n">
-        <v>6831123</v>
+        <v>6830964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041609</v>
+        <v>130041517</v>
       </c>
       <c r="B16" t="n">
-        <v>78498</v>
+        <v>78937</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475502</v>
+        <v>475474</v>
       </c>
       <c r="R16" t="n">
-        <v>6831264</v>
+        <v>6831123</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041446</v>
+        <v>130041494</v>
       </c>
       <c r="B17" t="n">
-        <v>79127</v>
+        <v>78938</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475549</v>
+        <v>475448</v>
       </c>
       <c r="R17" t="n">
-        <v>6830964</v>
+        <v>6830798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041517</v>
+        <v>130041609</v>
       </c>
       <c r="B18" t="n">
-        <v>78852</v>
+        <v>78583</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475474</v>
+        <v>475502</v>
       </c>
       <c r="R18" t="n">
-        <v>6831123</v>
+        <v>6831264</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130041514</v>
+        <v>130041497</v>
       </c>
       <c r="B19" t="n">
-        <v>78852</v>
+        <v>78938</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475402</v>
+        <v>475482</v>
       </c>
       <c r="R19" t="n">
-        <v>6830990</v>
+        <v>6831123</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130041510</v>
+        <v>130041610</v>
       </c>
       <c r="B20" t="n">
-        <v>78852</v>
+        <v>78583</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475448</v>
+        <v>475402</v>
       </c>
       <c r="R20" t="n">
-        <v>6830798</v>
+        <v>6830990</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130041610</v>
+        <v>130041510</v>
       </c>
       <c r="B21" t="n">
-        <v>78498</v>
+        <v>78937</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475402</v>
+        <v>475448</v>
       </c>
       <c r="R21" t="n">
-        <v>6830990</v>
+        <v>6830798</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2818,7 @@
         <v>130041504</v>
       </c>
       <c r="B22" t="n">
-        <v>81080</v>
+        <v>81165</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>130041511</v>
       </c>
       <c r="B23" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>130041496</v>
       </c>
       <c r="B24" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>130041559</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130041513</v>
+        <v>130041509</v>
       </c>
       <c r="B26" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475393</v>
+        <v>475484</v>
       </c>
       <c r="R26" t="n">
-        <v>6830875</v>
+        <v>6830883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130041509</v>
+        <v>130041513</v>
       </c>
       <c r="B27" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475484</v>
+        <v>475393</v>
       </c>
       <c r="R27" t="n">
-        <v>6830883</v>
+        <v>6830875</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,7 +3460,7 @@
         <v>130041440</v>
       </c>
       <c r="B28" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130041516</v>
+        <v>130041505</v>
       </c>
       <c r="B29" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3593,16 +3593,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475433</v>
+        <v>475552</v>
       </c>
       <c r="R29" t="n">
-        <v>6831092</v>
+        <v>6830976</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3639,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3649,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,7 +3679,7 @@
         <v>130041436</v>
       </c>
       <c r="B30" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,10 +3783,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130041505</v>
+        <v>130041561</v>
       </c>
       <c r="B31" t="n">
-        <v>78852</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,39 +3794,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475552</v>
+        <v>475554</v>
       </c>
       <c r="R31" t="n">
-        <v>6830976</v>
+        <v>6831117</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3890,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130041561</v>
+        <v>130041516</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>78937</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475554</v>
+        <v>475433</v>
       </c>
       <c r="R32" t="n">
-        <v>6831117</v>
+        <v>6831092</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4000,7 +4000,7 @@
         <v>130041438</v>
       </c>
       <c r="B33" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>130041560</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>130041451</v>
       </c>
       <c r="B35" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>130041454</v>
       </c>
       <c r="B36" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>130041512</v>
       </c>
       <c r="B37" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>130041453</v>
       </c>
       <c r="B38" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>130041452</v>
       </c>
       <c r="B39" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>130041607</v>
       </c>
       <c r="B40" t="n">
-        <v>78102</v>
+        <v>78187</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>130041557</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>130041558</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>130041503</v>
       </c>
       <c r="B43" t="n">
-        <v>81080</v>
+        <v>81165</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130044586</v>
+        <v>130044601</v>
       </c>
       <c r="B44" t="n">
-        <v>79714</v>
+        <v>79770</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5185,21 +5185,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475506</v>
+        <v>475483</v>
       </c>
       <c r="R44" t="n">
-        <v>6831387</v>
+        <v>6831369</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5278,7 +5278,7 @@
         <v>130044665</v>
       </c>
       <c r="B45" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130044601</v>
+        <v>130044586</v>
       </c>
       <c r="B46" t="n">
-        <v>79685</v>
+        <v>79799</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5391,21 +5391,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475483</v>
+        <v>475506</v>
       </c>
       <c r="R46" t="n">
-        <v>6831369</v>
+        <v>6831387</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5484,7 +5484,7 @@
         <v>130044604</v>
       </c>
       <c r="B47" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>130044657</v>
       </c>
       <c r="B48" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>130044587</v>
       </c>
       <c r="B49" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>130044636</v>
       </c>
       <c r="B50" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>130044631</v>
       </c>
       <c r="B51" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>130044585</v>
       </c>
       <c r="B52" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>130044628</v>
       </c>
       <c r="B53" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>130044669</v>
       </c>
       <c r="B54" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6289,10 +6289,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130044663</v>
+        <v>130044651</v>
       </c>
       <c r="B55" t="n">
-        <v>78852</v>
+        <v>79770</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6300,21 +6300,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475421</v>
+        <v>475450</v>
       </c>
       <c r="R55" t="n">
-        <v>6831144</v>
+        <v>6831186</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130044651</v>
+        <v>130044663</v>
       </c>
       <c r="B56" t="n">
-        <v>79685</v>
+        <v>78937</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6401,21 +6401,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6428,10 +6428,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475450</v>
+        <v>475421</v>
       </c>
       <c r="R56" t="n">
-        <v>6831186</v>
+        <v>6831144</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6494,7 +6494,7 @@
         <v>130044623</v>
       </c>
       <c r="B57" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>130044615</v>
       </c>
       <c r="B58" t="n">
-        <v>57845</v>
+        <v>57930</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>130044660</v>
       </c>
       <c r="B59" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -6289,10 +6289,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130044663</v>
+        <v>130044651</v>
       </c>
       <c r="B55" t="n">
-        <v>78937</v>
+        <v>79770</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6300,21 +6300,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475421</v>
+        <v>475450</v>
       </c>
       <c r="R55" t="n">
-        <v>6831144</v>
+        <v>6831186</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130044651</v>
+        <v>130044663</v>
       </c>
       <c r="B56" t="n">
-        <v>79770</v>
+        <v>78937</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6401,21 +6401,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6428,10 +6428,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475450</v>
+        <v>475421</v>
       </c>
       <c r="R56" t="n">
-        <v>6831186</v>
+        <v>6831144</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129996510</v>
+        <v>130041446</v>
       </c>
       <c r="B2" t="n">
-        <v>78937</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475476</v>
+        <v>475549</v>
       </c>
       <c r="R2" t="n">
-        <v>6831355</v>
+        <v>6830964</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,39 +775,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130041481</v>
+        <v>130041503</v>
       </c>
       <c r="B3" t="n">
-        <v>79204</v>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475411</v>
+        <v>475473</v>
       </c>
       <c r="R3" t="n">
-        <v>6830966</v>
+        <v>6831127</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130041437</v>
+        <v>130041504</v>
       </c>
       <c r="B4" t="n">
-        <v>79799</v>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475481</v>
+        <v>475493</v>
       </c>
       <c r="R4" t="n">
-        <v>6830882</v>
+        <v>6831320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130041441</v>
+        <v>130041557</v>
       </c>
       <c r="B5" t="n">
-        <v>79799</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475510</v>
+        <v>475553</v>
       </c>
       <c r="R5" t="n">
-        <v>6831109</v>
+        <v>6831206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130041456</v>
+        <v>130041558</v>
       </c>
       <c r="B6" t="n">
-        <v>79770</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475534</v>
+        <v>475533</v>
       </c>
       <c r="R6" t="n">
-        <v>6830960</v>
+        <v>6831180</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130041439</v>
+        <v>130041559</v>
       </c>
       <c r="B7" t="n">
-        <v>79799</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475435</v>
+        <v>475540</v>
       </c>
       <c r="R7" t="n">
-        <v>6831092</v>
+        <v>6831162</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130041480</v>
+        <v>130041560</v>
       </c>
       <c r="B8" t="n">
-        <v>79204</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475568</v>
+        <v>475581</v>
       </c>
       <c r="R8" t="n">
-        <v>6831221</v>
+        <v>6831068</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130041495</v>
+        <v>130041561</v>
       </c>
       <c r="B9" t="n">
-        <v>78938</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475417</v>
+        <v>475554</v>
       </c>
       <c r="R9" t="n">
-        <v>6831034</v>
+        <v>6831117</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130041455</v>
+        <v>130041480</v>
       </c>
       <c r="B10" t="n">
-        <v>79770</v>
+        <v>79351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475552</v>
+        <v>475568</v>
       </c>
       <c r="R10" t="n">
-        <v>6830976</v>
+        <v>6831221</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130041515</v>
+        <v>130041481</v>
       </c>
       <c r="B11" t="n">
-        <v>78937</v>
+        <v>79351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475417</v>
+        <v>475411</v>
       </c>
       <c r="R11" t="n">
-        <v>6831034</v>
+        <v>6830966</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130041493</v>
+        <v>130041609</v>
       </c>
       <c r="B12" t="n">
-        <v>78938</v>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475504</v>
+        <v>475502</v>
       </c>
       <c r="R12" t="n">
-        <v>6831263</v>
+        <v>6831264</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130041514</v>
+        <v>130041610</v>
       </c>
       <c r="B13" t="n">
-        <v>78937</v>
+        <v>78730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130041517</v>
+        <v>129996510</v>
       </c>
       <c r="B14" t="n">
-        <v>78937</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475474</v>
+        <v>475476</v>
       </c>
       <c r="R14" t="n">
-        <v>6831123</v>
+        <v>6831355</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,22 +2024,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130041446</v>
+        <v>130041505</v>
       </c>
       <c r="B15" t="n">
-        <v>79212</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,34 +2077,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475549</v>
+        <v>475552</v>
       </c>
       <c r="R15" t="n">
-        <v>6830964</v>
+        <v>6830976</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130041609</v>
+        <v>130041508</v>
       </c>
       <c r="B16" t="n">
-        <v>78583</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2189,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475502</v>
+        <v>475485</v>
       </c>
       <c r="R16" t="n">
-        <v>6831264</v>
+        <v>6831411</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130041457</v>
+        <v>130041509</v>
       </c>
       <c r="B17" t="n">
-        <v>79770</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475451</v>
+        <v>475484</v>
       </c>
       <c r="R17" t="n">
-        <v>6830833</v>
+        <v>6830883</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130041494</v>
+        <v>130041510</v>
       </c>
       <c r="B18" t="n">
-        <v>78938</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2494,10 +2499,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130041497</v>
+        <v>130041511</v>
       </c>
       <c r="B19" t="n">
-        <v>78938</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475482</v>
+        <v>475449</v>
       </c>
       <c r="R19" t="n">
-        <v>6831123</v>
+        <v>6830820</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2579,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130041510</v>
+        <v>130041512</v>
       </c>
       <c r="B20" t="n">
-        <v>78937</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475448</v>
+        <v>475395</v>
       </c>
       <c r="R20" t="n">
-        <v>6830798</v>
+        <v>6830844</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2676,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2686,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130041610</v>
+        <v>130041513</v>
       </c>
       <c r="B21" t="n">
-        <v>78583</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475402</v>
+        <v>475393</v>
       </c>
       <c r="R21" t="n">
-        <v>6830990</v>
+        <v>6830875</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130041504</v>
+        <v>130041514</v>
       </c>
       <c r="B22" t="n">
-        <v>81165</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475493</v>
+        <v>475402</v>
       </c>
       <c r="R22" t="n">
-        <v>6831320</v>
+        <v>6830990</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130041511</v>
+        <v>130041515</v>
       </c>
       <c r="B23" t="n">
-        <v>78937</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2957,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475449</v>
+        <v>475417</v>
       </c>
       <c r="R23" t="n">
-        <v>6830820</v>
+        <v>6831034</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2997,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3007,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130041496</v>
+        <v>130041516</v>
       </c>
       <c r="B24" t="n">
-        <v>78938</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,7 +3069,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475435</v>
+        <v>475433</v>
       </c>
       <c r="R24" t="n">
         <v>6831092</v>
@@ -3136,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130041559</v>
+        <v>130041517</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3152,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475540</v>
+        <v>475474</v>
       </c>
       <c r="R25" t="n">
-        <v>6831162</v>
+        <v>6831123</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3211,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3221,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130041509</v>
+        <v>130044657</v>
       </c>
       <c r="B26" t="n">
-        <v>78937</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3272,16 +3277,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Örnberget, Dlr</t>
+          <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475484</v>
+        <v>475450</v>
       </c>
       <c r="R26" t="n">
-        <v>6830883</v>
+        <v>6831186</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,49 +3319,40 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130041513</v>
+        <v>130044660</v>
       </c>
       <c r="B27" t="n">
-        <v>78937</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3379,16 +3378,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Örnberget, Dlr</t>
+          <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475393</v>
+        <v>475447</v>
       </c>
       <c r="R27" t="n">
-        <v>6830875</v>
+        <v>6831162</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,49 +3420,40 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130041440</v>
+        <v>130044663</v>
       </c>
       <c r="B28" t="n">
-        <v>79799</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,34 +3461,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Örnberget, Dlr</t>
+          <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475486</v>
+        <v>475421</v>
       </c>
       <c r="R28" t="n">
-        <v>6831120</v>
+        <v>6831144</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,49 +3521,40 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130041505</v>
+        <v>130041435</v>
       </c>
       <c r="B29" t="n">
-        <v>78937</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,39 +3562,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475552</v>
+        <v>475485</v>
       </c>
       <c r="R29" t="n">
-        <v>6830976</v>
+        <v>6831413</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3639,7 +3621,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3649,7 +3631,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3679,7 +3661,7 @@
         <v>130041436</v>
       </c>
       <c r="B30" t="n">
-        <v>79799</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3783,10 +3765,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130041516</v>
+        <v>130041437</v>
       </c>
       <c r="B31" t="n">
-        <v>78937</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3794,21 +3776,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3818,10 +3800,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475433</v>
+        <v>475481</v>
       </c>
       <c r="R31" t="n">
-        <v>6831092</v>
+        <v>6830882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,7 +3835,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3863,7 +3845,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3890,10 +3872,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130041561</v>
+        <v>130041438</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,21 +3883,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475554</v>
+        <v>475446</v>
       </c>
       <c r="R32" t="n">
-        <v>6831117</v>
+        <v>6830798</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3942,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3970,7 +3952,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3997,10 +3979,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130041438</v>
+        <v>130041439</v>
       </c>
       <c r="B33" t="n">
-        <v>79799</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4032,10 +4014,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475446</v>
+        <v>475435</v>
       </c>
       <c r="R33" t="n">
-        <v>6830798</v>
+        <v>6831092</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4067,7 +4049,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4077,7 +4059,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4104,10 +4086,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130041560</v>
+        <v>130041440</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4115,21 +4097,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4139,10 +4121,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475581</v>
+        <v>475486</v>
       </c>
       <c r="R34" t="n">
-        <v>6831068</v>
+        <v>6831120</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4174,7 +4156,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4184,7 +4166,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4211,10 +4193,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130041451</v>
+        <v>130041441</v>
       </c>
       <c r="B35" t="n">
-        <v>79770</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4222,21 +4204,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4246,10 +4228,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475501</v>
+        <v>475510</v>
       </c>
       <c r="R35" t="n">
-        <v>6831374</v>
+        <v>6831109</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,7 +4263,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4291,7 +4273,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4318,10 +4300,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130041454</v>
+        <v>130044586</v>
       </c>
       <c r="B36" t="n">
-        <v>79770</v>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4329,34 +4311,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Örnberget, Dlr</t>
+          <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475497</v>
+        <v>475506</v>
       </c>
       <c r="R36" t="n">
-        <v>6831311</v>
+        <v>6831387</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4386,49 +4371,40 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130041512</v>
+        <v>130044587</v>
       </c>
       <c r="B37" t="n">
-        <v>78937</v>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4436,34 +4412,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Örnberget, Dlr</t>
+          <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475395</v>
+        <v>475483</v>
       </c>
       <c r="R37" t="n">
-        <v>6830844</v>
+        <v>6831369</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4493,49 +4472,40 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130041453</v>
+        <v>130044628</v>
       </c>
       <c r="B38" t="n">
-        <v>79770</v>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4543,34 +4513,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Örnberget, Dlr</t>
+          <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475492</v>
+        <v>475460</v>
       </c>
       <c r="R38" t="n">
-        <v>6831322</v>
+        <v>6831267</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4600,49 +4573,40 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130041452</v>
+        <v>130044669</v>
       </c>
       <c r="B39" t="n">
-        <v>79770</v>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4650,34 +4614,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Örnberget, Dlr</t>
+          <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475483</v>
+        <v>475501</v>
       </c>
       <c r="R39" t="n">
-        <v>6831329</v>
+        <v>6831118</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4707,39 +4674,30 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4749,7 +4707,7 @@
         <v>130041607</v>
       </c>
       <c r="B40" t="n">
-        <v>78187</v>
+        <v>78334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4853,10 +4811,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130041557</v>
+        <v>130044665</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,34 +4822,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Örnberget, Dlr</t>
+          <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475553</v>
+        <v>475435</v>
       </c>
       <c r="R41" t="n">
-        <v>6831206</v>
+        <v>6831137</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4921,19 +4887,9 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4948,22 +4904,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130041558</v>
+        <v>130044615</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>58057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4971,34 +4927,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Örnberget, Dlr</t>
+          <t>Trubbingen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475533</v>
+        <v>475444</v>
       </c>
       <c r="R42" t="n">
-        <v>6831180</v>
+        <v>6831288</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5028,19 +4992,9 @@
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5055,22 +5009,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130041503</v>
+        <v>130041492</v>
       </c>
       <c r="B43" t="n">
-        <v>81165</v>
+        <v>79085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5078,21 +5032,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5102,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475473</v>
+        <v>475485</v>
       </c>
       <c r="R43" t="n">
-        <v>6831127</v>
+        <v>6831411</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5137,7 +5091,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5147,7 +5101,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5174,10 +5128,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130044665</v>
+        <v>130041493</v>
       </c>
       <c r="B44" t="n">
-        <v>57826</v>
+        <v>79085</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5185,42 +5139,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475435</v>
+        <v>475504</v>
       </c>
       <c r="R44" t="n">
-        <v>6831137</v>
+        <v>6831263</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5250,9 +5196,19 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5267,22 +5223,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130044586</v>
+        <v>130041494</v>
       </c>
       <c r="B45" t="n">
-        <v>79799</v>
+        <v>79085</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5290,37 +5246,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475506</v>
+        <v>475448</v>
       </c>
       <c r="R45" t="n">
-        <v>6831387</v>
+        <v>6830798</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5350,40 +5303,49 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130044601</v>
+        <v>130041495</v>
       </c>
       <c r="B46" t="n">
-        <v>79770</v>
+        <v>79085</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5391,37 +5353,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475483</v>
+        <v>475417</v>
       </c>
       <c r="R46" t="n">
-        <v>6831369</v>
+        <v>6831034</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5451,40 +5410,49 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130044604</v>
+        <v>130041496</v>
       </c>
       <c r="B47" t="n">
-        <v>78938</v>
+        <v>79085</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5510,19 +5478,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475483</v>
+        <v>475435</v>
       </c>
       <c r="R47" t="n">
-        <v>6831369</v>
+        <v>6831092</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5552,40 +5517,49 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130044657</v>
+        <v>130041497</v>
       </c>
       <c r="B48" t="n">
-        <v>78937</v>
+        <v>79085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5593,37 +5567,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475450</v>
+        <v>475482</v>
       </c>
       <c r="R48" t="n">
-        <v>6831186</v>
+        <v>6831123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5653,40 +5624,49 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130044587</v>
+        <v>130044584</v>
       </c>
       <c r="B49" t="n">
-        <v>79799</v>
+        <v>79085</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5674,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5721,10 +5701,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475483</v>
+        <v>475500</v>
       </c>
       <c r="R49" t="n">
-        <v>6831369</v>
+        <v>6831409</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5784,10 +5764,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130044636</v>
+        <v>130044585</v>
       </c>
       <c r="B50" t="n">
-        <v>78938</v>
+        <v>79085</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,10 +5802,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475460</v>
+        <v>475506</v>
       </c>
       <c r="R50" t="n">
-        <v>6831232</v>
+        <v>6831387</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5885,10 +5865,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130044631</v>
+        <v>130044604</v>
       </c>
       <c r="B51" t="n">
-        <v>79770</v>
+        <v>79085</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5896,21 +5876,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5923,10 +5903,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475472</v>
+        <v>475483</v>
       </c>
       <c r="R51" t="n">
-        <v>6831247</v>
+        <v>6831369</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5986,10 +5966,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130044585</v>
+        <v>130044623</v>
       </c>
       <c r="B52" t="n">
-        <v>78938</v>
+        <v>79085</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6024,10 +6004,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475506</v>
+        <v>475460</v>
       </c>
       <c r="R52" t="n">
-        <v>6831387</v>
+        <v>6831267</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6087,10 +6067,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130044628</v>
+        <v>130044636</v>
       </c>
       <c r="B53" t="n">
-        <v>79799</v>
+        <v>79085</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,21 +6078,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6128,7 +6108,7 @@
         <v>475460</v>
       </c>
       <c r="R53" t="n">
-        <v>6831267</v>
+        <v>6831232</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6188,10 +6168,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130044669</v>
+        <v>130041451</v>
       </c>
       <c r="B54" t="n">
-        <v>79799</v>
+        <v>79917</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6199,37 +6179,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>475501</v>
       </c>
       <c r="R54" t="n">
-        <v>6831118</v>
+        <v>6831374</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6259,40 +6236,49 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130044651</v>
+        <v>130041452</v>
       </c>
       <c r="B55" t="n">
-        <v>79770</v>
+        <v>79917</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6318,19 +6304,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475450</v>
+        <v>475483</v>
       </c>
       <c r="R55" t="n">
-        <v>6831186</v>
+        <v>6831329</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6360,40 +6343,49 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130044663</v>
+        <v>130041453</v>
       </c>
       <c r="B56" t="n">
-        <v>78937</v>
+        <v>79917</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6401,37 +6393,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475421</v>
+        <v>475492</v>
       </c>
       <c r="R56" t="n">
-        <v>6831144</v>
+        <v>6831322</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6461,40 +6450,49 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130044623</v>
+        <v>130041454</v>
       </c>
       <c r="B57" t="n">
-        <v>78938</v>
+        <v>79917</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6502,37 +6500,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475460</v>
+        <v>475497</v>
       </c>
       <c r="R57" t="n">
-        <v>6831267</v>
+        <v>6831311</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6562,40 +6557,49 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130044660</v>
+        <v>130041455</v>
       </c>
       <c r="B58" t="n">
-        <v>78937</v>
+        <v>79917</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6603,37 +6607,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475447</v>
+        <v>475552</v>
       </c>
       <c r="R58" t="n">
-        <v>6831162</v>
+        <v>6830976</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6663,83 +6664,84 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130044615</v>
+        <v>130041456</v>
       </c>
       <c r="B59" t="n">
-        <v>57930</v>
+        <v>79917</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Trubbingen, Dlr</t>
+          <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>475444</v>
+        <v>475534</v>
       </c>
       <c r="R59" t="n">
-        <v>6831288</v>
+        <v>6830960</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6769,9 +6771,19 @@
           <t>2025-12-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6786,15 +6798,425 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130041457</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>475451</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6830833</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130044601</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>475483</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6831369</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
           <t>Håkan Thenander</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
+      <c r="AX61" t="inlineStr">
         <is>
           <t>Håkan Thenander</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130044631</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>475472</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6831247</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130044651</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Trubbingen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>475450</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6831186</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53688-2025 artfynd.xlsx
+++ b/artfynd/A 53688-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041446</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041503</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041504</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041557</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041558</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041559</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041560</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041561</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041480</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041481</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041609</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041610</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996510</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041505</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041508</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041509</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2496,6 +2581,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041510</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2603,6 +2693,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041511</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2710,6 +2805,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041512</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041513</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2924,6 +3029,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041514</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041515</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3138,6 +3253,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041516</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3245,6 +3365,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041517</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3346,6 +3471,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044657</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3447,6 +3577,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044660</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3548,6 +3683,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044663</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3655,6 +3795,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041435</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3762,6 +3907,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041436</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3869,6 +4019,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041437</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3976,6 +4131,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041438</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4083,6 +4243,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041439</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4190,6 +4355,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041440</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4297,6 +4467,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041441</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4398,6 +4573,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044586</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4499,6 +4679,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044587</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4600,6 +4785,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044628</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4701,6 +4891,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044669</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4808,6 +5003,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041607</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4913,6 +5113,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044665</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5018,6 +5223,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044615</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5125,6 +5335,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041492</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5232,6 +5447,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041493</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5339,6 +5559,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041494</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5446,6 +5671,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041495</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5553,6 +5783,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041496</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5660,6 +5895,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041497</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5761,6 +6001,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044584</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5862,6 +6107,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044585</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5963,6 +6213,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044604</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6064,6 +6319,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044623</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6165,6 +6425,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044636</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6272,6 +6537,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041451</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6379,6 +6649,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041452</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6486,6 +6761,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041453</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6593,6 +6873,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041454</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6700,6 +6985,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041455</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6807,6 +7097,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041456</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6914,6 +7209,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130041457</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7015,6 +7315,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044601</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7116,6 +7421,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044631</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7217,8 +7527,77 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130044651</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>